--- a/output/full_scan/batch_seq6_2026-07-01.xlsx
+++ b/output/full_scan/batch_seq6_2026-07-01.xlsx
@@ -428,17 +428,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="7" customWidth="1" min="11" max="11"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>6241</v>
+        <v>6164</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>738.621459530299</v>
+        <v>1149.004555380289</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.95</v>
+        <v>14.45</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.99154817264373</v>
+        <v>64.19660103342197</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45.02204749107158</v>
+        <v>24.422017115806</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.8827429617838248</v>
+        <v>3.117428779567349</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.0763253454022061</v>
+        <v>0.0415695602328159</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6173</v>
+        <v>6438</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>686.9301181196128</v>
+        <v>1099.615485774782</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>341.5</v>
+        <v>167.5</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,82 +605,6177 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>69.97409133723403</v>
+        <v>58.96137756998598</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>35.79933627998187</v>
+        <v>22.86993889135089</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.4833882633378319</v>
+        <v>3.660446123607158</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>-0.6595023413231189</v>
+        <v>1.686333220624384</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
+        <v>6271</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>同欣電</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1046.046844516594</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>63.26784823466573</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>27.94287895035762</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>3.423241093584283</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>2.037823737725488</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>6288</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>聯嘉</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>993.7637113435804</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>66.6786233352334</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>25.09979732413489</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>3.476371134358034</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>0.1973288870834002</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>6257</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>矽格</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>993.6302114048336</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>245</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>61.1723651065079</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>24.38809215579037</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>1.667307974048068</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.709618102392616</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6259</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>百徽</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>910.6404119016668</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>62.89056585308838</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>43.60979234965392</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1.556360516445243</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.3793673916086852</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>6196</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>帆宣</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>878.3839392617648</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>571</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>63.36883903502394</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>34.50849048090856</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>1.33271786224056</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>-3.15191927123184</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>6182</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>合晶</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>868.4276811667777</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>71.23435332298213</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>39.37402339395187</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.6057449238336136</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>1.018865429046688</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>6409</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>旭隼</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>857.0774603492926</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>75.31293766361098</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>45.28485678734602</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1.307746034929261</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>17.4167427224213</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>6173</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>信昌電</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>856.9301181196128</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>341.5</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>69.97409133500486</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>35.79933613560438</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.4833882633378319</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>-0.6595023410846466</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>6274</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>台燿</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>834.0264853294934</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1690</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>55.27503869343997</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>25.89261195438868</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.8530446347970968</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>-19.10172951735916</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>6213</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>聯茂</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>802.7183684265768</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>68.32297136775234</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>22.2398110488302</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.182171211861295</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>9.796500688833421</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>6174</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>安碁</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>801.6226000946258</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>60.403627496282</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>37.63943749136917</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.8947849543865217</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>-0.3864363217529192</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6446</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>藥華藥</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>791.5298429880366</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1360</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>83.51442164252865</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>52.54240755137281</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>0.8764784046462022</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>27.22573705913751</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>784</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>17.05</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>66.90516331997985</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>8.432700829929916</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>18.73711823121604</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>0.9645165839068812</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, cci_momentum, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>6191</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>精成科</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>774.0972750856209</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>55.95048295100115</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>23.84524214107388</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>1.20972750856209</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>0.7103848385557965</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>6292</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>迅德</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>770.6906765093401</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>59.47717721876558</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>26.85605166564604</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>2.55797190026193</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>-0.4791229186330281</v>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>6224</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>聚鼎</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>766.423368858847</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>56.06147701412978</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>18.986723363304</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>2.421047413221358</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>-0.4436752858814874</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>6435</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>大中</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>753.1389051764494</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>357</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>66.71612118140403</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>35.90498701628619</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>2.945079294473636</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>2.816670867104257</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>倍微</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>746.0805084253324</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>39.35</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>62.70928752905518</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>51.30772506514623</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>0.5468657625937521</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>0.07155971458104909</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>6241</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>鑫永洋</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>738.621459530299</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>64.99154816903723</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>45.02204746895255</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.8827429617838248</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>0.0763253454212868</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>6190</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>萬泰科</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>724.80975842904</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>56.42809980025581</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>19.44937716993052</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.338135727002277</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>-0.0468150097979713</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>6477</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>安集</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>713.061098296531</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>34.25</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>56.36504360484464</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>14.24651518822602</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>3.684377342450974</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>0.1502386810545656</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>macd_golden_cross, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>6243</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>迅杰</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>712.6616305098246</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>61.03102284775456</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>32.07512464262793</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.2828281140685205</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>0.6778976328564217</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>6223</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>711.3513200733687</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>6695</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>57.8865760002601</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>21.65218736775119</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.6539345330071581</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>-38.3012819007335</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>6226</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>光鼎</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>698.7015604009653</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>24.25</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>88.41927771228514</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>32.80538277872462</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.4701560400965282</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>1.190130953211748</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>6175</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>立敦</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>672.4171512583902</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>55.91311035211116</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>39.12683407324779</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.7934162372546688</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>-0.9522344195010451</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>6220</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>岳豐</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>668.6763084668432</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>47.20757556475208</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>48.94928190564362</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.3345267374860823</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>-0.4656943176247516</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>6207</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>雷科</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>666.698723924348</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>62.56948586967786</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>56.14075816946976</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.4916409127513492</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>-2.287828300580355</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>6204</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>艾華</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>664.1743662380225</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>60.6593926286853</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>35.17857023736045</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>1.145456453977426</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>-0.198364913378894</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>6189</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>651.2347890452828</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>53.20213539317669</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>21.25421356321914</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.9145945945945946</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>-0.5321489542048115</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>6197</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>640.3998791479668</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>348</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>60.9384298430877</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>43.13633316980702</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>0.460725875203842</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>-3.152685476804159</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>6284</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>佳邦</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>636.2010215436054</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>54.80243738917856</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>34.34767472090441</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>1.357590294833289</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>-0.7606870850447116</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>6411</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>晶焱</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>604.0178454587498</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>49.83148439586294</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>27.18342200590536</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.8354331464906853</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>-0.971026154924168</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>6217</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>中探針</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>601.7109425979371</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>263</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>51.37041472288101</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>14.72439905129141</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>1.260964692557534</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>0.9557895419072352</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>6465</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>威潤</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>600.8838327668591</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>54.54171853326233</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>32.22730603831423</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.4720464388676389</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>-0.746584448551995</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>6278</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>599.0681072767601</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>52.10924721452577</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>18.85687400656885</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>1.395430961627721</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>-0.934556156737042</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>6432</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>今展科</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>594.8286465930446</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>55.7120729314491</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>36.52369721770854</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.386549309512477</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>-1.107159160108729</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>6168</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>宏齊</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>581.8507900884985</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>30.15</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>53.58745046148366</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>26.72205331768939</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.5665886862394945</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>0.1533934789620781</v>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>6239</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>力成</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>574.30367722302</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>335.5</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>53.9328756499687</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>27.66469017292132</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.8387440655056775</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>-5.298965254351797</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>6209</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>今國光</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>566.3893749404479</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>45.07973078722377</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>34.00195462008053</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.2620168269148767</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>-2.014537478404237</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>6215</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>和椿</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>551.7209806379304</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>47.1330113379972</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>20.35416495079278</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>1.075736135000957</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>-0.2781428455242829</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>6415</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>矽力*-KY</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>533.4497821311514</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>53.05534449973612</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>23.23228571870875</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.3060684861014868</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>-3.852742823459543</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>6222</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>立軒</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>533.0020771878646</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>55.31531659195931</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>28.16739708955538</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.0601811850601511</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>0.0722708651206511</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, bb_squeeze_breakout, cci_momentum</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>6261</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>久元</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>512.798503789705</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>41.29886776917418</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>20.89907323753884</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.4111287167006284</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>-0.5298193390864143</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
         <v>6187</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D4" s="2" t="n">
+      <c r="C47" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>487.9647556939715</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E47" s="2" t="n">
         <v>1065</v>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>47.41603770281965</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>13.47802386393965</v>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>47.41603769995413</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>13.47802383446753</v>
+      </c>
+      <c r="J47" s="2" t="n">
         <v>0.6809354622770293</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>-13.56095215953936</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="L47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>-13.56095215829925</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>6202</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>盛群</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>484.4815340595002</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>53.34328910181193</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>29.57810890191267</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.7752539082167694</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>-0.1582427618405524</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>6265</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>方土昶</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>479.6122351769386</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>43.2664310565482</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>26.17522138612712</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.5132683159024398</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>-1.250841666381262</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>6451</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>訊芯-KY</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>478.564729534222</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>524</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>44.51054230477622</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>29.92436674081438</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.7443172256044909</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>-8.295154155846509</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>6269</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>台郡</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>476.3149143810094</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>43.67776637200085</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>26.77671384544451</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.8314914381009437</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>-1.467259734845845</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>6472</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>保瑞</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>472.5270735954312</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>423.5</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>56.05546785045067</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>26.50854962050951</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.4511445850834361</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>2.211725252381452</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>6412</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>群電</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>467.1023922547922</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>52.14681214020965</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>15.68569957983745</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.7098759676883517</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>-0.12628690232176</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>6462</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>神盾</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>457.7817998320531</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>47.03062515237616</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>18.18330322189205</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.5271307413753858</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>0.3612854158614929</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>6423</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>億而得-創</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>436.3346790572493</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>41.67126052167178</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>27.8588202888354</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>1.968972041683101</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>0.6108878034748413</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>6166</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>凌華</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>432.186760953926</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>46.63412681144418</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>53.98695384770833</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>0.8811126260880344</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>-2.87601222563282</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>6208</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>日揚</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>428.5479161513186</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>92.7</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>49.7600710812179</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>19.21820949758732</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.6134907887683532</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>-0.1988655924639832</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>6234</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>高僑</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>420.8979267014931</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>48.99731611443617</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>13.89227577059466</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>1.044689833516394</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>0.1896124571268371</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>6237</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>驊訊</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>420.1727090823595</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>42.86341326631825</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>17.3547038055385</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.4419984631300917</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>-0.4433157913283294</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>6449</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>鈺邦</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>419.5767524316517</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>349</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>48.12693831631155</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>27.47219267535259</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.489986574306034</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>-14.76949587821286</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>6246</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>臺龍</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>417.3273767497413</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>44.13238324556232</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>24.04487230668342</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.8327376749741368</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>0.0497021744794008</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>6282</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>康舒</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>413.7496989909894</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>50.05857360417906</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>26.6276576251504</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.5719650846764003</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>-0.658996062450084</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>6275</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>元山</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>412.823875268339</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>48.96807421758321</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>15.62306305469679</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.3708033621987057</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>0.0572753177272823</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>精誠</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>412.3484784076358</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>44.96265624957258</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>19.78856549097434</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.6291507426122556</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>-1.787949253883245</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>6244</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>茂迪</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>409.6936532055718</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>43.00469122470141</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>14.09304324150515</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>0.3992533270197221</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>-0.3159315735518961</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>6228</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>全譜</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>408.8027012493159</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>50.9130419157314</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>4.676494570774923</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>3.143423575676818</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>-0.0206849607271122</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>6405</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>悅城</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>408.2578454687417</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>42.25777410906488</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>22.08584966288725</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.6720345067978258</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>-1.734471718496931</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>6419</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>京晨科</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>404.6721266229675</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>51.08671132220627</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>11.45172539517128</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>0.5168031404924588</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>-0.2347140782389518</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>6414</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>樺漢</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>404.3647960705383</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>370.5</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>51.46324818630704</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>18.24910059753213</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.4815029137203708</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>-3.375307908926036</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>6279</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>胡連</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>396.770771498977</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>45.0553894661952</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>14.70354300488947</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>0.648352106849547</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>-0.6575473237630997</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>6198</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>瑞築</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>391.4889575842293</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>51.41609654321596</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>6.365219867547538</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1.610581089135277</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>0.1433277745955029</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>6418</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>詠昇</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>390.519363276854</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>48.47106767735192</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>19.37969302346044</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.4607332085519415</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>-0.1266227475852397</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>6229</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>研通</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>385.4194197829224</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>49.72118853845777</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>11.95403297031459</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.392274374329784</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>-0.0751095089405415</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>6291</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沛亨</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>373.2343193186674</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>535</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>47.36716367015808</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>16.0129896148025</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>1.23499244835355</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>-3.08354875329556</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>6225</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>天瀚</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>372.9730157490018</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>47.57518626239259</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>12.01291551616952</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>0.3137671930900322</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>-0.2060567987949632</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, stronger_than_market</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>6417</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>韋僑</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>371.5273128583388</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>47.68242909098425</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>12.18655012028238</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1.717078590039007</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>-0.5829898643369835</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>6245</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>立端</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>367.121484571983</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>44.89569354758832</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>16.89070516160312</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>0.6719192193450682</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>-0.368998324744319</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>6277</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>宏正</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>354.6872775849168</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>39.6566768920206</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>29.47879035178573</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>0.3913025625711566</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>-0.5316155634060562</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>6464</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>台數科</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>353.4499900537649</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>38.25209116692518</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>20.45873827365762</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>0.2888321779140142</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>-0.0937986126042111</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>6233</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>旺玖</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>352.9835477134012</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>48.61903039746831</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>13.07129152607895</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.5501670533191203</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>0.145923671280321</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>6176</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>瑞儀</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>346.5123465128918</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>33.92848209995199</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>23.18146468998765</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>0.5850213110959476</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>-0.1434771737562368</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>6263</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>普萊德</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>339.852779334588</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>45.95172037409601</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>12.51899652671132</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>0.3566087323707268</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>-0.8036931982858095</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>6290</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>良維</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>338.2205258985863</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>50.51586553756052</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>12.12023861893723</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>0.9316764576698878</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>-2.395699877946068</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>6170</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>統振</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>337.8354296031034</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>52.8252894588271</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>15.02814217214455</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.7249920211007143</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>-0.0454292426430439</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, dealer_buy_3d, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>6177</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>達麗</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>334.039248945171</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>46.05</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>51.18016315201938</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>19.98655687333765</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>1.090505930765084</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>-0.1664155191329598</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>6227</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>茂綸</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>331.4999963400928</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>47.91437424770382</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>16.07334191441742</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.2905682960976714</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>-1.542394989250901</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6192</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>巨路</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>330.5876731559098</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>120.5</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>46.3958152221073</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>20.70559319916345</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>0.2342752653471674</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>0.1798297027949271</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>6474</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>華豫寧</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>323.8705776460706</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>50.96966549779766</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>14.05852608792551</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>0.6642044125261617</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>0.3732878349617923</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>6426</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>統新</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>311.3765601775941</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>38.24008043655811</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>17.00587304078735</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>0.4158279440991435</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>-1.848733246486402</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>6285</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>啟碁</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>302.3844125102026</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>249</v>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>43.20118045872981</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>20.31623927044167</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>0.8342811629708642</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>-3.68002012030997</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>6167</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>久正</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>302.3366713643655</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>53.95248265165389</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>10.33118658080579</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>0.9578777220228268</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>0.0501500824898394</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>6194</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>育富</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>296.4902596000462</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>48.14697009718342</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>12.45881203388126</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>3.006310627952469</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>-0.0215442547363339</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>6185</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>幃翔</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>296.0356924411781</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>49.57463541993472</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>16.21807587670664</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.4409069905289032</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>-0.0136127611924368</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>6218</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>豪勉</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>288.5592844265291</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>47.05322518130048</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>14.85867077594713</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.3661077854177604</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>0.1284486411378484</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>6183</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>關貿</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>286.0280274826578</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>47.01251746619867</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>12.57834826387511</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>0.4159910773070763</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>0.0450590439026635</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>6210</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>慶生</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>280.729728532344</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>41.62343524652525</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>17.84051718437608</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.6405312878066359</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>-0.1106241116713725</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>6205</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>詮欣</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>261.4810155524379</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>41.33701266755665</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>12.76025301087169</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.348648024101217</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>-1.121122931130132</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>6456</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>GIS-KY</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>258.5207761100022</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>39.44449706329829</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>13.95539445099143</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>0.9551029543808012</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>-1.185489637798912</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>6283</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>淳安</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>255.1696969620568</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>40.97285375107724</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>15.26458766221305</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.412955058123172</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>-0.1640005044244759</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>6216</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>居易</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>249.0367660520776</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>46.14549957777615</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>15.53405444060634</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.8426612982022326</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>-0.0044630366419767</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>6442</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>245.8582231906481</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>1575</v>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>37.59142374297551</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>12.16732842403614</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.977903504249062</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>-39.83126587195346</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>6416</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>瑞祺電通</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>244.1060687716986</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>37.6217579260472</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>23.29851444940102</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.4262454672992637</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>-0.4771455251090517</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>6206</v>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>飛捷</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>240.4876211401944</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>43.32997948725007</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>15.29810155809063</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>0.5253739853827896</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>-1.297040953534669</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>6443</v>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>元晶</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>239.9572040953913</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>36.67325724196115</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>16.35055232676177</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>0.2918776180301809</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>-0.5632063277131887</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>6188</v>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>廣明</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>233.5934972882134</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>43.61617296920127</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>16.96430375002238</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.019530190693522</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>-0.1675903840304582</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>6485</v>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>點序</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>226.0658545133442</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>38.20555396737418</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>17.66934669254061</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>0.2121570681909147</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>-1.271100114545946</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>6230</v>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>尼得科超眾</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>219.5535182709345</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>38.69085861113424</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>13.63493119909926</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.4036560315654139</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>-0.6958023028539477</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>6184</v>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>大豐電</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>219.4816110306621</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>19.43056869789691</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>31.51690460123539</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>0.6347758920877941</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>-0.3807399711098079</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>6266</v>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>泰詠</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>218.9718306438354</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>34.26240588649756</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>25.78004331466512</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>0.5047721481904205</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>-0.1072344820419771</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>6281</v>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>全國電</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>215.9391219407148</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>47.29356380550259</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>9.57544455328078</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>0.4565755215469808</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>-0.009295231737458699</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>6165</v>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>浪凡</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>203.5972192864634</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>45.23552074406175</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>12.91561534329787</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>0.475049354164414</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>-0.1182820673565301</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>6272</v>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>驊陞</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>202.5647420568985</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>38.83340000357609</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>23.74480047506529</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>0.396898466754551</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>-0.3893846569633938</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>6287</v>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>元隆</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>200.5981307237124</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>59.44129991636949</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>17.15900332080148</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.3819364013941486</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>0.0075007321009113</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>rsi_strong, avoid_chase, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>6201</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>亞弘電</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>187.4883632411248</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>46.3461711343815</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>13.85712233321674</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>0.5602306832225034</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>0.07016124524269191</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>6276</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>安鈦克</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>179.8658808134565</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>34.27583809320797</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>27.88428588890369</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.9378423006574762</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.1159990168303151</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6441</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>廣錠</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>175.3079429845373</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>45.4726872792851</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>10.99759411117991</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.6247187325043594</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.0094384074679564</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6470</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>宇智</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>151.3222278525021</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>48.35</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>44.43227036411378</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>12.67733470624046</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.5998620138423577</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.1635691113292505</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>131.7907563236263</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>42.22684637024335</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>17.60455830328953</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>0.4557920996894631</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
+        <v>-0.187554455126493</v>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>6235</v>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>華孚</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>107.4229004658216</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>40.46921630333858</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>12.08742757576581</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.7774050202334636</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N119" s="2" t="n">
+        <v>-0.1330166433064077</v>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
